--- a/docs/Mapping_casi_uso/riconoscimenti/Rico_022.xlsx
+++ b/docs/Mapping_casi_uso/riconoscimenti/Rico_022.xlsx
@@ -3915,10 +3915,10 @@
         <v>114</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>115</v>
@@ -3927,7 +3927,7 @@
         <v>98</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>30</v>
